--- a/outputs/53117.xlsx
+++ b/outputs/53117.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="12">
   <si>
     <t xml:space="preserve">Customer</t>
   </si>
@@ -157,7 +157,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -168,11 +171,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -184,7 +187,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -196,15 +199,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -212,11 +215,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -224,11 +227,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -488,7 +491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="n">
         <v>1065414</v>
       </c>
@@ -498,12 +501,11 @@
       <c r="C2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="11" t="str">
-        <f aca="false" t="array" ref="D2:D2">IF(C2&lt;&gt;"US",C2,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A2)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A2)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
-      </c>
-    </row>
-    <row r="3" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>5</v>
       </c>
@@ -513,12 +515,11 @@
       <c r="C3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="str">
-        <f aca="false" t="array" ref="D3:D3">IF(C3&lt;&gt;"US",C3,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A3)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A3)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="4" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -528,9 +529,8 @@
       <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="14" t="str">
-        <f aca="false" t="array" ref="D4:D4">IF(C4&lt;&gt;"US",C4,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A4)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A4)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
+      <c r="D4" s="14" t="n">
+        <v>4995</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>8</v>
@@ -539,7 +539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
@@ -549,12 +549,11 @@
       <c r="C5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="11" t="str">
-        <f aca="false" t="array" ref="D5:D5">IF(C5&lt;&gt;"US",C5,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A5)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A5)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D5" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
@@ -564,12 +563,11 @@
       <c r="C6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="11" t="str">
-        <f aca="false" t="array" ref="D6:D6">IF(C6&lt;&gt;"US",C6,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A6)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A6)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="7" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D6" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="n">
         <v>1001130</v>
       </c>
@@ -579,12 +577,11 @@
       <c r="C7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="11" t="str">
-        <f aca="false" t="array" ref="D7:D7">IF(C7&lt;&gt;"US",C7,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A7)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A7)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -594,12 +591,11 @@
       <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="11" t="str">
-        <f aca="false" t="array" ref="D8:D8">IF(C8&lt;&gt;"US",C8,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A8)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A8)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D8" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -609,9 +605,8 @@
       <c r="C9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="14" t="str">
-        <f aca="false" t="array" ref="D9:D9">IF(C9&lt;&gt;"US",C9,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A9)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A9)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
+      <c r="D9" s="14" t="n">
+        <v>141500</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>8</v>
@@ -620,7 +615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -630,12 +625,11 @@
       <c r="C10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="11" t="str">
-        <f aca="false" t="array" ref="D10:D10">IF(C10&lt;&gt;"US",C10,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A10)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A10)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D10" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -645,12 +639,11 @@
       <c r="C11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="11" t="str">
-        <f aca="false" t="array" ref="D11:D11">IF(C11&lt;&gt;"US",C11,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A11)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A11)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D11" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -660,15 +653,14 @@
       <c r="C12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="14" t="str">
-        <f aca="false" t="array" ref="D12:D12">IF(C12&lt;&gt;"US",C12,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A12)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A12)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
+      <c r="D12" s="14" t="n">
+        <v>141500</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1001130</v>
       </c>
@@ -678,15 +670,14 @@
       <c r="C13" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="14" t="str">
-        <f aca="false" t="array" ref="D13:D13">IF(C13&lt;&gt;"US",C13,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A13)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A13)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
+      <c r="D13" s="14" t="n">
+        <v>141500</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -696,12 +687,11 @@
       <c r="C14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="11" t="str">
-        <f aca="false" t="array" ref="D14:D14">IF(C14&lt;&gt;"US",C14,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A14)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A14)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D14" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -711,12 +701,11 @@
       <c r="C15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="11" t="str">
-        <f aca="false" t="array" ref="D15:D15">IF(C15&lt;&gt;"US",C15,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A15)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A15)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D15" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -726,15 +715,14 @@
       <c r="C16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="14" t="str">
-        <f aca="false" t="array" ref="D16:D16">IF(C16&lt;&gt;"US",C16,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A16)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A16)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
+      <c r="D16" s="14" t="n">
+        <v>43485</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -744,12 +732,11 @@
       <c r="C17" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="11" t="str">
-        <f aca="false" t="array" ref="D17:D17">IF(C17&lt;&gt;"US",C17,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A17)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A17)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D17" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -759,12 +746,11 @@
       <c r="C18" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="11" t="str">
-        <f aca="false" t="array" ref="D18:D18">IF(C18&lt;&gt;"US",C18,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A18)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A18)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D18" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1019559</v>
       </c>
@@ -774,15 +760,14 @@
       <c r="C19" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="14" t="str">
-        <f aca="false" t="array" ref="D19:D19">IF(C19&lt;&gt;"US",C19,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A19)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A19)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
+      <c r="D19" s="14" t="n">
+        <v>43485</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -792,12 +777,11 @@
       <c r="C20" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="3" t="str">
-        <f aca="false" t="array" ref="D20:D20">IF(C20&lt;&gt;"US",C20,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A20)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A20)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -807,12 +791,11 @@
       <c r="C21" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="3" t="str">
-        <f aca="false" t="array" ref="D21:D21">IF(C21&lt;&gt;"US",C21,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A21)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A21)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D21" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -822,15 +805,14 @@
       <c r="C22" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="16" t="str">
-        <f aca="false" t="array" ref="D22:D22">IF(C22&lt;&gt;"US",C22,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A22)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A22)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>China</v>
+      <c r="D22" s="16" t="n">
+        <v>160195</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -840,12 +822,11 @@
       <c r="C23" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="3" t="str">
-        <f aca="false" t="array" ref="D23:D23">IF(C23&lt;&gt;"US",C23,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A23)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A23)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Japan</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -855,12 +836,11 @@
       <c r="C24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="3" t="str">
-        <f aca="false" t="array" ref="D24:D24">IF(C24&lt;&gt;"US",C24,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A24)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A24)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -870,15 +850,14 @@
       <c r="C25" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="16" t="str">
-        <f aca="false" t="array" ref="D25:D25">IF(C25&lt;&gt;"US",C25,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A25)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A25)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>China</v>
+      <c r="D25" s="16" t="n">
+        <v>160195</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -888,12 +867,11 @@
       <c r="C26" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="3" t="str">
-        <f aca="false" t="array" ref="D26:D26">IF(C26&lt;&gt;"US",C26,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A26)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A26)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>China</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>1029551</v>
       </c>
@@ -903,9 +881,8 @@
       <c r="C27" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="3" t="str">
-        <f aca="false" t="array" ref="D27:D27">IF(C27&lt;&gt;"US",C27,INDEX($C$2:$C$27,MATCH(MAX(IF(($A$2:$A$27=A27)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27)),IF(($A$2:$A$27=A27)*($C$2:$C$27&lt;&gt;"US"),$B$2:$B$27),0)))</f>
-        <v>China</v>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
